--- a/tiflow-core/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow-core/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T19:28:42+00:00</t>
+    <t>2026-05-20T05:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow-core/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T05:35:28+00:00</t>
+    <t>2026-05-21T06:36:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow-core/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T06:44:28+00:00</t>
+    <t>2026-05-22T08:34:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow-core/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T08:34:46+00:00</t>
+    <t>2026-05-22T11:07:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
